--- a/artfynd/A 19352-2024 artfynd.xlsx
+++ b/artfynd/A 19352-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117766608</v>
+        <v>117766612</v>
       </c>
       <c r="B3" t="n">
-        <v>90499</v>
+        <v>100097</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,30 +789,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565894</v>
+        <v>565910</v>
       </c>
       <c r="R3" t="n">
-        <v>6707438</v>
+        <v>6707268</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117766612</v>
+        <v>117766608</v>
       </c>
       <c r="B4" t="n">
-        <v>100097</v>
+        <v>90499</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,30 +900,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565910</v>
+        <v>565894</v>
       </c>
       <c r="R4" t="n">
-        <v>6707268</v>
+        <v>6707438</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 19352-2024 artfynd.xlsx
+++ b/artfynd/A 19352-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>117766612</v>
       </c>
       <c r="B3" t="n">
-        <v>100097</v>
+        <v>100099</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>117766608</v>
       </c>
       <c r="B4" t="n">
-        <v>90499</v>
+        <v>90501</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
